--- a/processed_ruby_restored_xlsx/sc142_みるく２：恋人化.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc142_みるく２：恋人化.ss.xlsx
@@ -950,8 +950,8 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Hearing something like "it's fun to always be together
-with everyone" is such a happy thing.</t>
+          <t>Hearing something like "it's fun to always be
+together with everyone" is such a happy thing.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -981,9 +981,9 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>「There are all sorts of events during summer break, so
-I think we’ll be asking Janitor-sensei to help out as
-well.」</t>
+          <t>「There are all sorts of events during summer break,
+so I think we’ll be asking Janitor-sensei to help out
+as well.」</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1058,7 +1058,8 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Suddenly put on the spot, I hastily sat up straighter.</t>
+          <t>Suddenly put on the spot, I hastily sat up
+straighter.</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1181,8 +1182,8 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan-sensei, forgetting her role as a teacher, is
-thrilled at the idea of everyone's first summer
+          <t>Nono-chan-sensei, forgetting her role as a teacher,
+is thrilled at the idea of everyone's first summer
 vacation together.</t>
         </is>
       </c>
@@ -1763,8 +1764,8 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>I shouted loudly to blow away Rurichiyo-chan's worried
-look.</t>
+          <t>I shouted loudly to blow away Rurichiyo-chan's
+worried look.</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1795,8 +1796,8 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>I was an adult so I'd be fine, and I had things to do,
-so I probably wouldn't cry from loneliness.</t>
+          <t>I was an adult so I'd be fine, and I had things to
+do, so I probably wouldn't cry from loneliness.</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1857,8 +1858,8 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>At that moment, Miru-chan's lonely-looking eyes caught
-my attention.</t>
+          <t>At that moment, Miru-chan's lonely-looking eyes
+caught my attention.</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1873,8 +1874,9 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>There were no more classes today, so after the closing
-ceremony and homeroom she headed straight home.</t>
+          <t>There were no more classes today, so after the
+closing ceremony and homeroom she headed straight
+home.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2011,7 +2013,8 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>「...So, are you sad when Miru and the others go away？」</t>
+          <t>「...So, are you sad when Miru and the others go
+away？」</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2056,8 +2059,8 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>Carried along by Miru-chan's mood, I nod before I even
-realize it.</t>
+          <t>Carried along by Miru-chan's mood, I nod before I
+even realize it.</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2867,8 +2870,8 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>There's no way only Miru-chan would stay behind in the
-dormitory—there's no such convenient arrangement…</t>
+          <t>There's no way only Miru-chan would stay behind in
+the dormitory—there's no such convenient arrangement…</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3113,8 +3116,8 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>Mind you, it was only a parting of a few days. Nothing
-to get that serious over.</t>
+          <t>Mind you, it was only a parting of a few days.
+Nothing to get that serious over.</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3482,8 +3485,9 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan smiled a little sheepishly, then immediately
-went back to an amused, carefree expression.</t>
+          <t>Miru-chan smiled a little sheepishly, then
+immediately went back to an amused, carefree
+expression.</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3817,8 +3821,8 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>Meanwhile, Miru-chan's mother, completely unconcerned,
-left Miru-chan in my care.</t>
+          <t>Meanwhile, Miru-chan's mother, completely
+unconcerned, left Miru-chan in my care.</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -4029,8 +4033,8 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>As I sat there choking up with tears, Miru-chan tugged
-at the hem of my shirt.</t>
+          <t>As I sat there choking up with tears, Miru-chan
+tugged at the hem of my shirt.</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4302,8 +4306,8 @@
       <c r="B251" s="1" t="inlineStr">
         <is>
           <t>I know it’s silly to be so happy about something so
-minor, but when other kids are around I have to listen
-to everyone’s opinions.</t>
+minor, but when other kids are around I have to
+listen to everyone’s opinions.</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4851,8 +4855,8 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>By the time I thought I should warn her, Miru-chan had
-been caught by the water and fallen over.</t>
+          <t>By the time I thought I should warn her, Miru-chan
+had been caught by the water and fallen over.</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -5175,8 +5179,8 @@
       <c r="B308" s="1" t="inlineStr">
         <is>
           <t>It's not exactly poetic, but as someone who does the
-laundry every day, it's the kind of thing that bothers
-me.</t>
+laundry every day, it's the kind of thing that
+bothers me.</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5313,7 +5317,8 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>「Ehehe... but, with this, is it okay if I get wet...？」</t>
+          <t>「Ehehe... but, with this, is it okay if I get
+wet...？」</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5511,9 +5516,9 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>While hanging Miru-chan's clothes so they wouldn't get
-wrinkled, I was called by Miru-chan frolicking in the
-sea.</t>
+          <t>While hanging Miru-chan's clothes so they wouldn't
+get wrinkled, I was called by Miru-chan frolicking in
+the sea.</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5789,8 +5794,8 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>Half teasing, half scolding, I said that and Miru-chan
-leaned down and slipped out of my arms.</t>
+          <t>Half teasing, half scolding, I said that and
+Miru-chan leaned down and slipped out of my arms.</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -5942,8 +5947,8 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>Once her feet hit the ground, Miru-chan shook her head
-like a puppy shaking water off.</t>
+          <t>Once her feet hit the ground, Miru-chan shook her
+head like a puppy shaking water off.</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -6064,8 +6069,8 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>Maybe she can tell from the mood, Miru-chan just looks
-bashful.</t>
+          <t>Maybe she can tell from the mood, Miru-chan just
+looks bashful.</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -6232,7 +6237,8 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>When I said something lewd, I got splashed with water.</t>
+          <t>When I said something lewd, I got splashed with
+water.</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6368,8 +6374,8 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t>As we went back to our childhood and enjoyed splashing
-each other, Miru-chan gave a little shiver.</t>
+          <t>As we went back to our childhood and enjoyed
+splashing each other, Miru-chan gave a little shiver.</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -6444,8 +6450,8 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>No sooner had she said it than she started kicking her
-feet.</t>
+          <t>No sooner had she said it than she started kicking
+her feet.</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -6522,8 +6528,8 @@
       <c r="B396" s="1" t="inlineStr">
         <is>
           <t>Even if you've been playing and you're all warm,
-there's nothing you can do because the moisture steals
-heat as it evaporates.</t>
+there's nothing you can do because the moisture
+steals heat as it evaporates.</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6583,8 +6589,8 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan presses her between-the-legs and shifts from
-foot to foot.</t>
+          <t>Miru-chan presses her between-the-legs and shifts
+from foot to foot.</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6903,8 +6909,8 @@
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t>「I'm not teasing you. There's no bathroom, so it can't
-be helped, okay？」</t>
+          <t>「I'm not teasing you. There's no bathroom, so it
+can't be helped, okay？」</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6994,8 +7000,8 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>「W-what do you mean... It's so embarrassing to do this
-dressed like this...」</t>
+          <t>「W-what do you mean... It's so embarrassing to do
+this dressed like this...」</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7025,7 +7031,8 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t>I nodded inside, but I didn't want to say it out loud.</t>
+          <t>I nodded inside, but I didn't want to say it out
+loud.</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -7040,7 +7047,8 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t>Honestly, I kind of want to see Miru-chan being shy...</t>
+          <t>Honestly, I kind of want to see Miru-chan being
+shy...</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -7652,8 +7660,8 @@
       <c r="B470" s="1" t="inlineStr">
         <is>
           <t>Given how things were going, I thought it might be
-better to play it off, but my mouth just blurts things
-out on its own.</t>
+better to play it off, but my mouth just blurts
+things out on its own.</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -8154,8 +8162,8 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t>Maybe she'd given up, or maybe she'd reached her limit
-— she said it with a shy, sulky tone.</t>
+          <t>Maybe she'd given up, or maybe she'd reached her
+limit — she said it with a shy, sulky tone.</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -8459,8 +8467,8 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>...Would that be similar to being so nervous you can't
-get an erection？</t>
+          <t>...Would that be similar to being so nervous you
+can't get an erection？</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8841,8 +8849,8 @@
       </c>
       <c r="B548" s="1" t="inlineStr">
         <is>
-          <t>She was probably remembering that incident in the bath
-the other day.</t>
+          <t>She was probably remembering that incident in the
+bath the other day.</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -8903,8 +8911,8 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>I lifted my hand a little and searched a bit above her
-slit.</t>
+          <t>I lifted my hand a little and searched a bit above
+her slit.</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -9165,7 +9173,8 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan’s scent grew stronger and more intoxicating.</t>
+          <t>Miru-chan’s scent grew stronger and more
+intoxicating.</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -9347,8 +9356,8 @@
       </c>
       <c r="B581" s="1" t="inlineStr">
         <is>
-          <t>And the splash as it hit the surface made me melt with
-pleasure.</t>
+          <t>And the splash as it hit the surface made me melt
+with pleasure.</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -9582,8 +9591,8 @@
       </c>
       <c r="B596" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan pulled away from me, hoisted her panties up,
-and gave me a pouty look.</t>
+          <t>Miru-chan pulled away from me, hoisted her panties
+up, and gave me a pouty look.</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -9887,8 +9896,8 @@
       </c>
       <c r="B616" s="1" t="inlineStr">
         <is>
-          <t>「Aaah... you'll catch a cold like this. Come over here
-for a sec...！」</t>
+          <t>「Aaah... you'll catch a cold like this. Come over
+here for a sec...！」</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -9950,9 +9959,9 @@
       </c>
       <c r="B620" s="1" t="inlineStr">
         <is>
-          <t>「Phew... I'm glad I hung it out to dry. You'll catch a
-cold, so take off what you're wearing now and change
-into this.」</t>
+          <t>「Phew... I'm glad I hung it out to dry. You'll catch
+a cold, so take off what you're wearing now and
+change into this.」</t>
         </is>
       </c>
       <c r="C620" t="n">
@@ -10152,8 +10161,8 @@
       </c>
       <c r="B633" s="1" t="inlineStr">
         <is>
-          <t>But in the end, we’d ended up playing in the water, so
-nothing really changed.</t>
+          <t>But in the end, we’d ended up playing in the water,
+so nothing really changed.</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -10547,8 +10556,8 @@
       </c>
       <c r="B659" s="1" t="inlineStr">
         <is>
-          <t>Since it was just the two of us, there was no one else
-to talk to.</t>
+          <t>Since it was just the two of us, there was no one
+else to talk to.</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -10884,8 +10893,8 @@
       </c>
       <c r="B681" s="1" t="inlineStr">
         <is>
-          <t>Even at her size, she's such a girl about these little
-subtleties...</t>
+          <t>Even at her size, she's such a girl about these
+little subtleties...</t>
         </is>
       </c>
       <c r="C681" t="n">
@@ -12367,8 +12376,8 @@
       </c>
       <c r="B778" s="1" t="inlineStr">
         <is>
-          <t>I stopped thinking about it because just thinking made
-me feel embarrassed.</t>
+          <t>I stopped thinking about it because just thinking
+made me feel embarrassed.</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -12962,8 +12971,8 @@
       </c>
       <c r="B817" s="1" t="inlineStr">
         <is>
-          <t>I parted my lips slightly, and Miru-chan’s tongue slid
-into my mouth.</t>
+          <t>I parted my lips slightly, and Miru-chan’s tongue
+slid into my mouth.</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -13132,8 +13141,8 @@
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
-          <t>Then, right away Miru-chan's tongue was entwining with
-mine.</t>
+          <t>Then, right away Miru-chan's tongue was entwining
+with mine.</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -13287,8 +13296,8 @@
       </c>
       <c r="B838" s="1" t="inlineStr">
         <is>
-          <t>「Ammuuuh？ Nmm, chu-ku！ Ahf, chu, chujyu！ Djuku, chu...
-nfuuhh...！」</t>
+          <t>「Ammuuuh？ Nmm, chu-ku！ Ahf, chu, chujyu！ Djuku,
+chu... nfuuhh...！」</t>
         </is>
       </c>
       <c r="C838" t="n">
@@ -13793,8 +13802,8 @@
       </c>
       <c r="B871" s="1" t="inlineStr">
         <is>
-          <t>I read the card's instruction while making small talk,
-as if to shake off my embarrassment.</t>
+          <t>I read the card's instruction while making small
+talk, as if to shake off my embarrassment.</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -13932,7 +13941,8 @@
       </c>
       <c r="B880" s="1" t="inlineStr">
         <is>
-          <t>「Miru-chan. I'm going to… give the instruction, okay？」</t>
+          <t>「Miru-chan. I'm going to… give the instruction,
+okay？」</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -14023,8 +14033,8 @@
       </c>
       <c r="B886" s="1" t="inlineStr">
         <is>
-          <t>When hugged, Miru-chan, who was shy at first, lets out
-a laugh.</t>
+          <t>When hugged, Miru-chan, who was shy at first, lets
+out a laugh.</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -14328,8 +14338,8 @@
       </c>
       <c r="B906" s="1" t="inlineStr">
         <is>
-          <t>I wonder if I wouldn't have been caught if I'd smelled
-it more quietly？</t>
+          <t>I wonder if I wouldn't have been caught if I'd
+smelled it more quietly？</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -14404,8 +14414,8 @@
       </c>
       <c r="B911" s="1" t="inlineStr">
         <is>
-          <t>Then, like always, she concentrates as she shakes them
-and lands on the Special Box twice in a row.</t>
+          <t>Then, like always, she concentrates as she shakes
+them and lands on the Special Box twice in a row.</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -14889,8 +14899,8 @@
       </c>
       <c r="B943" s="1" t="inlineStr">
         <is>
-          <t>When I gently patted her head, Miru-chan brightened up
-and made a happy little snort.</t>
+          <t>When I gently patted her head, Miru-chan brightened
+up and made a happy little snort.</t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -14950,7 +14960,8 @@
       </c>
       <c r="B947" s="1" t="inlineStr">
         <is>
-          <t>Feeling mellow, I said that and leaned my face closer.</t>
+          <t>Feeling mellow, I said that and leaned my face
+closer.</t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -15087,8 +15098,8 @@
       </c>
       <c r="B956" s="1" t="inlineStr">
         <is>
-          <t>On the contrary, she kissed me back naturally and even
-showed me a smile.</t>
+          <t>On the contrary, she kissed me back naturally and
+even showed me a smile.</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -15133,7 +15144,8 @@
       </c>
       <c r="B959" s="1" t="inlineStr">
         <is>
-          <t>「Onii-chan… your face is getting all slack, you know？」</t>
+          <t>「Onii-chan… your face is getting all slack, you
+know？」</t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -15178,8 +15190,8 @@
       </c>
       <c r="B962" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan hurriedly moved away, and I grabbed the dice
-like nothing had happened.</t>
+          <t>Miru-chan hurriedly moved away, and I grabbed the
+dice like nothing had happened.</t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -15528,9 +15540,9 @@
       </c>
       <c r="B985" s="1" t="inlineStr">
         <is>
-          <t>Even if the kiss had been okay because Miru-chan wrote
-the same thing, what terrible timing to get this
-one...</t>
+          <t>Even if the kiss had been okay because Miru-chan
+wrote the same thing, what terrible timing to get
+this one...</t>
         </is>
       </c>
       <c r="C985" t="n">
@@ -15818,8 +15830,8 @@
       </c>
       <c r="B1004" s="1" t="inlineStr">
         <is>
-          <t>When my hand touched her chest, Miru-chan flinched—her
-whole body trembling.</t>
+          <t>When my hand touched her chest, Miru-chan
+flinched—her whole body trembling.</t>
         </is>
       </c>
       <c r="C1004" t="n">
@@ -15971,8 +15983,9 @@
       </c>
       <c r="B1014" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan suddenly brushed my hand away as if bouncing
-off, pouted while yelling, and grabbed the dice.</t>
+          <t>Miru-chan suddenly brushed my hand away as if
+bouncing off, pouted while yelling, and grabbed the
+dice.</t>
         </is>
       </c>
       <c r="C1014" t="n">
@@ -16386,8 +16399,8 @@
       </c>
       <c r="B1041" s="1" t="inlineStr">
         <is>
-          <t>Yeah, that really might’ve been a card that put her on
-guard.</t>
+          <t>Yeah, that really might’ve been a card that put her
+on guard.</t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -16403,8 +16416,8 @@
       <c r="B1042" s="1" t="inlineStr">
         <is>
           <t>It wasn’t a command like patting the head or a tight
-hug—those are the kinds that make you feel each other,
-after all.</t>
+hug—those are the kinds that make you feel each
+other, after all.</t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -17274,8 +17287,8 @@
       </c>
       <c r="B1099" s="1" t="inlineStr">
         <is>
-          <t>But she's just unbearably cute when she's honest about
-her feelings！</t>
+          <t>But she's just unbearably cute when she's honest
+about her feelings！</t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -17595,8 +17608,8 @@
       </c>
       <c r="B1120" s="1" t="inlineStr">
         <is>
-          <t>She seems to be doing anything to distract herself for
-the time being.</t>
+          <t>She seems to be doing anything to distract herself
+for the time being.</t>
         </is>
       </c>
       <c r="C1120" t="n">
@@ -17656,7 +17669,8 @@
       </c>
       <c r="B1124" s="1" t="inlineStr">
         <is>
-          <t>「Yay！ At this rate, Miru's totally gonna win, y'know？」</t>
+          <t>「Yay！ At this rate, Miru's totally gonna win,
+y'know？」</t>
         </is>
       </c>
       <c r="C1124" t="n">
@@ -18125,8 +18139,8 @@
       </c>
       <c r="B1155" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan answers like she always does, but there's no
-strength in her voice.</t>
+          <t>Miru-chan answers like she always does, but there's
+no strength in her voice.</t>
         </is>
       </c>
       <c r="C1155" t="n">
@@ -18752,8 +18766,8 @@
       </c>
       <c r="B1196" s="1" t="inlineStr">
         <is>
-          <t>When I gently laid a hand on her shoulder, Miru-chan's
-voice popped.</t>
+          <t>When I gently laid a hand on her shoulder,
+Miru-chan's voice popped.</t>
         </is>
       </c>
       <c r="C1196" t="n">
@@ -19765,7 +19779,8 @@
       </c>
       <c r="B1262" s="1" t="inlineStr">
         <is>
-          <t>Carefully so as not to break her, slowly... slowly....</t>
+          <t>Carefully so as not to break her, slowly...
+slowly....</t>
         </is>
       </c>
       <c r="C1262" t="n">
@@ -20101,8 +20116,8 @@
       </c>
       <c r="B1284" s="1" t="inlineStr">
         <is>
-          <t>「Aha... Onii-chan, you're like someone from a manga...
-it must feel good, right？」</t>
+          <t>「Aha... Onii-chan, you're like someone from a
+manga... it must feel good, right？」</t>
         </is>
       </c>
       <c r="C1284" t="n">
@@ -20178,8 +20193,8 @@
       </c>
       <c r="B1289" s="1" t="inlineStr">
         <is>
-          <t>「So, s-so, would Miru... be all like, ‘I’m gonna come~
-I’m gonna come~’？」</t>
+          <t>「So, s-so, would Miru... be all like, ‘I’m gonna
+come~ I’m gonna come~’？」</t>
         </is>
       </c>
       <c r="C1289" t="n">
@@ -20255,7 +20270,8 @@
       </c>
       <c r="B1294" s="1" t="inlineStr">
         <is>
-          <t>「Oh, really...？ Hehe, I might be a little excited...？」</t>
+          <t>「Oh, really...？ Hehe, I might be a little
+excited...？」</t>
         </is>
       </c>
       <c r="C1294" t="n">
@@ -20668,9 +20684,9 @@
       </c>
       <c r="B1321" s="1" t="inlineStr">
         <is>
-          <t>Her insides are tight all the way through, yet somehow
-they have a softness that doesn't make it feel that
-way.</t>
+          <t>Her insides are tight all the way through, yet
+somehow they have a softness that doesn't make it
+feel that way.</t>
         </is>
       </c>
       <c r="C1321" t="n">
@@ -20854,8 +20870,8 @@
       </c>
       <c r="B1333" s="1" t="inlineStr">
         <is>
-          <t>Just as my penis told me, it was buried all the way to
-the base.</t>
+          <t>Just as my penis told me, it was buried all the way
+to the base.</t>
         </is>
       </c>
       <c r="C1333" t="n">
@@ -21068,8 +21084,8 @@
       </c>
       <c r="B1347" s="1" t="inlineStr">
         <is>
-          <t>「Whew... yeah... Miru's okay... it just hurts a little
-bit...」</t>
+          <t>「Whew... yeah... Miru's okay... it just hurts a
+little bit...」</t>
         </is>
       </c>
       <c r="C1347" t="n">
@@ -21115,8 +21131,8 @@
       </c>
       <c r="B1350" s="1" t="inlineStr">
         <is>
-          <t>「Oh... then, shall we stay still until you get used to
-it？」</t>
+          <t>「Oh... then, shall we stay still until you get used
+to it？」</t>
         </is>
       </c>
       <c r="C1350" t="n">
@@ -21849,8 +21865,8 @@
       </c>
       <c r="B1398" s="1" t="inlineStr">
         <is>
-          <t>I was feeling awkward inside, so I answered exactly as
-Miru-chan asked.</t>
+          <t>I was feeling awkward inside, so I answered exactly
+as Miru-chan asked.</t>
         </is>
       </c>
       <c r="C1398" t="n">
@@ -22018,8 +22034,8 @@
       </c>
       <c r="B1409" s="1" t="inlineStr">
         <is>
-          <t>When I swayed my hips, Miru-chan mirrored my movements
-exactly.</t>
+          <t>When I swayed my hips, Miru-chan mirrored my
+movements exactly.</t>
         </is>
       </c>
       <c r="C1409" t="n">
@@ -22828,8 +22844,8 @@
       </c>
       <c r="B1462" s="1" t="inlineStr">
         <is>
-          <t>「Nn…nn！ Uwa…aaah！ There… there too… it’s good！ It’s so
-good…！」</t>
+          <t>「Nn…nn！ Uwa…aaah！ There… there too… it’s good！ It’s
+so good…！」</t>
         </is>
       </c>
       <c r="C1462" t="n">
@@ -23180,8 +23196,8 @@
       </c>
       <c r="B1485" s="1" t="inlineStr">
         <is>
-          <t>Before I knew it, the bunk bed was creaking as I moved
-rhythmically.</t>
+          <t>Before I knew it, the bunk bed was creaking as I
+moved rhythmically.</t>
         </is>
       </c>
       <c r="C1485" t="n">
@@ -23425,8 +23441,8 @@
       </c>
       <c r="B1501" s="1" t="inlineStr">
         <is>
-          <t>I say that and, half out of embarrassment, I wiggle my
-hips.</t>
+          <t>I say that and, half out of embarrassment, I wiggle
+my hips.</t>
         </is>
       </c>
       <c r="C1501" t="n">
@@ -23672,8 +23688,8 @@
       </c>
       <c r="B1517" s="1" t="inlineStr">
         <is>
-          <t>Because she now understands the pleasure of sex on her
-skin, the embarrassment only seems to grow.</t>
+          <t>Because she now understands the pleasure of sex on
+her skin, the embarrassment only seems to grow.</t>
         </is>
       </c>
       <c r="C1517" t="n">
@@ -23887,7 +23903,8 @@
       </c>
       <c r="B1531" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ Nnh, nnh, nngh！？ Hah, haa… n-ah, ah, ah！ Nngh！？」</t>
+          <t>「Huh？ Nnh, nnh, nngh！？ Hah, haa… n-ah, ah, ah！
+Nngh！？」</t>
         </is>
       </c>
       <c r="C1531" t="n">
@@ -24072,8 +24089,8 @@
       </c>
       <c r="B1543" s="1" t="inlineStr">
         <is>
-          <t>Even if she's being led on, I think it's true that she
-actually feels good.</t>
+          <t>Even if she's being led on, I think it's true that
+she actually feels good.</t>
         </is>
       </c>
       <c r="C1543" t="n">
@@ -24667,8 +24684,8 @@
       </c>
       <c r="B1582" s="1" t="inlineStr">
         <is>
-          <t>My orgasm and Miru-chan’s body twitching were in sync…
-I could tell, but her reactions were a bit too
+          <t>My orgasm and Miru-chan’s body twitching were in
+sync… I could tell, but her reactions were a bit too
 intense.</t>
         </is>
       </c>
@@ -24715,7 +24732,8 @@
       </c>
       <c r="B1585" s="1" t="inlineStr">
         <is>
-          <t>「Uuh... uhh...！  Uhh...！  Huu, huuu... uuh... ... ...」</t>
+          <t>「Uuh... uhh...！  Uhh...！  Huu, huuu... uuh... ...
+...」</t>
         </is>
       </c>
       <c r="C1585" t="n">
@@ -25141,8 +25159,8 @@
       </c>
       <c r="B1613" s="1" t="inlineStr">
         <is>
-          <t>She responded better than I expected, and it felt like
-she was back to her usual Miru-chan smile.</t>
+          <t>She responded better than I expected, and it felt
+like she was back to her usual Miru-chan smile.</t>
         </is>
       </c>
       <c r="C1613" t="n">
@@ -25356,8 +25374,8 @@
       </c>
       <c r="B1627" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan had realized during sex that both of us feel
-good together, and she was happy about it... .</t>
+          <t>Miru-chan had realized during sex that both of us
+feel good together, and she was happy about it... .</t>
         </is>
       </c>
       <c r="C1627" t="n">

--- a/processed_ruby_restored_xlsx/sc142_みるく２：恋人化.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc142_みるく２：恋人化.ss.xlsx
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>When Rurichiyo agreed, Rin started teasing me this
+          <t>When Rurichiyo agreed, Rin started teasing him this
 time.</t>
         </is>
       </c>
@@ -1658,7 +1658,7 @@
       <c r="B78" s="1" t="inlineStr">
         <is>
           <t>But since it might pass as a joke and win back the
-teasing mood, I decided to play along a little.</t>
+teasing mood, he decided to play along a little.</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1796,8 +1796,8 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>I was an adult so I'd be fine, and I had things to
-do, so I probably wouldn't cry from loneliness.</t>
+          <t>He was an adult so he'd be fine, and he had things to
+do, so he probably wouldn't cry from loneliness.</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1813,7 +1813,7 @@
       <c r="B88" s="1" t="inlineStr">
         <is>
           <t>Still, as a feeling, it seemed like a hollow hole
-would open up inside me.</t>
+would open up inside him.</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1859,7 +1859,7 @@
       <c r="B91" s="1" t="inlineStr">
         <is>
           <t>At that moment, Miru-chan's lonely-looking eyes
-caught my attention.</t>
+caught his attention.</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1892,8 +1892,8 @@
       <c r="B93" s="1" t="inlineStr">
         <is>
           <t>She'd come back in the morning, eaten lunch in the
-living room, and while I was cleaning up, Miru-chan
-came over to me alone.</t>
+living room, and while he was cleaning up, Miru-chan
+came over to him alone.</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>「Wooooah！ I have to contact them right now！」</t>
+          <t>Wooooah！ I have to contact them right now！</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>「Sigh... I feel kind of tired...」</t>
+          <t>Sigh... I feel kind of tired...</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>「Arriiiival！　Nnnnng…！」</t>
+          <t>Arriiiival！　Nnnnng…！</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>Seeing Miru-chan in her underwear, I think, damn.</t>
+          <t>Seeing Miru-chan in her underwear, he thinks, damn.</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5287,7 +5287,7 @@
       <c r="B315" s="1" t="inlineStr">
         <is>
           <t>Did I make her take her clothes off in a place like
-this... will she hate me...？</t>
+this... will she hate me...？"</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>「So it's gone cold after all.」</t>
+          <t>So it's gone cold after all.</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="B407" s="1" t="inlineStr">
         <is>
-          <t>「Eh？　Eeh！？」</t>
+          <t>「Eh？　Eeh！？</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -7200,8 +7200,8 @@
       </c>
       <c r="B440" s="1" t="inlineStr">
         <is>
-          <t>「So, do you want me to put you in the pee-pee pose to
-make it easier to pee？」</t>
+          <t>So, do you want me to put you in the pee-pee pose to
+make it easier to pee？</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t>「Not that either—nooo！」</t>
+          <t>Not that either—nooo！</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>「Hey, not that—don't go sniffing me！」</t>
+          <t>Hey, not that—don't go sniffing me！</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -7842,8 +7842,8 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>I keep goofing off, and she thinks she can shake me
-off by herself.</t>
+          <t>I keep goofing off, and they think they can shake me
+off by themselves.</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="B484" s="1" t="inlineStr">
         <is>
-          <t>「Muuuuhhh！  Uuuuhhhhuuuuhhh！」</t>
+          <t>Muuuuhhh！  Uuuuhhhhuuuuhhh！</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -9820,7 +9820,7 @@
       <c r="B611" s="1" t="inlineStr">
         <is>
           <t>As for that, I'll honestly apologize, but... is it
-okay that I touched between your legs...？</t>
+okay that I touched between your legs...？"</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -9959,9 +9959,9 @@
       </c>
       <c r="B620" s="1" t="inlineStr">
         <is>
-          <t>「Phew... I'm glad I hung it out to dry. You'll catch
-a cold, so take off what you're wearing now and
-change into this.」</t>
+          <t>Phew... I'm glad I hung it out to dry. You'll catch a
+cold, so take off what you're wearing now and change
+into this.</t>
         </is>
       </c>
       <c r="C620" t="n">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="B802" s="1" t="inlineStr">
         <is>
-          <t>I said that and, closing my eyes, started thinking.</t>
+          <t>She says that and, closing her eyes, starts thinking.</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -12955,8 +12955,8 @@
       </c>
       <c r="B816" s="1" t="inlineStr">
         <is>
-          <t>「Nn... chu！ Re-ru, nnh...！ Kuchu, chu... chuku, nn,
-rero, rero...！」</t>
+          <t>Nn... chu！ Re-ru, nnh...！ Kuchu, chu... chuku, nn,
+rero, rero...！</t>
         </is>
       </c>
       <c r="C816" t="n">
@@ -13296,8 +13296,8 @@
       </c>
       <c r="B838" s="1" t="inlineStr">
         <is>
-          <t>「Ammuuuh？ Nmm, chu-ku！ Ahf, chu, chujyu！ Djuku,
-chu... nfuuhh...！」</t>
+          <t>Ammuuuh？ Nmm, chu-ku！ Ahf, chu, chujyu！ Djuku, chu...
+nfuuhh...！</t>
         </is>
       </c>
       <c r="C838" t="n">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B889" s="1" t="inlineStr">
         <is>
-          <t>「Is this okay？」</t>
+          <t>Is this okay？</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="B891" s="1" t="inlineStr">
         <is>
-          <t>「No—！ A little longer…」</t>
+          <t>No—！ A little longer…</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -14139,7 +14139,7 @@
       </c>
       <c r="B893" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, yeah...」</t>
+          <t>Yeah, yeah...</t>
         </is>
       </c>
       <c r="C893" t="n">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B940" s="1" t="inlineStr">
         <is>
-          <t>「Alright... there we go, there we go. Gooood...」</t>
+          <t>Alright... there we go, there we go. Gooood...</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="B942" s="1" t="inlineStr">
         <is>
-          <t>「Hmm… fufufuun…！」</t>
+          <t>Hmm… fufufuun…！</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="B946" s="1" t="inlineStr">
         <is>
-          <t>「Miru-chan's orders are cute, aren't they？」</t>
+          <t>Miru-chan's orders are cute, aren't they？</t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B949" s="1" t="inlineStr">
         <is>
-          <t>「Eh? What, like that~…?」</t>
+          <t>Eh? What, like that~…?</t>
         </is>
       </c>
       <c r="C949" t="n">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="B951" s="1" t="inlineStr">
         <is>
-          <t>「...smooch！」</t>
+          <t>...smooch！</t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="B954" s="1" t="inlineStr">
         <is>
-          <t>「Smooch！ Uf… uhi！ Ehehehe！」</t>
+          <t>Smooch！ Uf… uhi！ Ehehehe！</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -15144,8 +15144,7 @@
       </c>
       <c r="B959" s="1" t="inlineStr">
         <is>
-          <t>「Onii-chan… your face is getting all slack, you
-know？」</t>
+          <t>Onii-chan… your face is getting all slack, you know？</t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -15175,7 +15174,7 @@
       </c>
       <c r="B961" s="1" t="inlineStr">
         <is>
-          <t>「...Well then, it's my turn again.」</t>
+          <t>...Well then, it's my turn again.</t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -15221,7 +15220,7 @@
       </c>
       <c r="B964" s="1" t="inlineStr">
         <is>
-          <t>「Hmmmm？ Another special order？」</t>
+          <t>Hmmmm？ Another special order？</t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -15251,7 +15250,7 @@
       </c>
       <c r="B966" s="1" t="inlineStr">
         <is>
-          <t>「Yeees, here it is~！ I wonder what it is this time~？」</t>
+          <t>Yeees, here it is~！ I wonder what it is this time~？</t>
         </is>
       </c>
       <c r="C966" t="n">
@@ -16796,7 +16795,7 @@
       </c>
       <c r="B1067" s="1" t="inlineStr">
         <is>
-          <t>...To say it to her face took guts, and it was
+          <t>...To say it to their face took guts, and it was
 embarrassing too.</t>
         </is>
       </c>
@@ -18963,7 +18962,8 @@
       </c>
       <c r="B1209" s="1" t="inlineStr">
         <is>
-          <t>When I touch her chest, it shudders as if convulsing.</t>
+          <t>When he touches her chest, it shudders as if
+convulsing.</t>
         </is>
       </c>
       <c r="C1209" t="n">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="B1231" s="1" t="inlineStr">
         <is>
-          <t>When the tip of my penis glided along the space
+          <t>When the tip of his penis glided along the space
 between her legs, Miru-chan tensed up and let out a
 long breath.</t>
         </is>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="B1236" s="1" t="inlineStr">
         <is>
-          <t>As I toyed her slit with the tip, Miru-chan answered
+          <t>As he toyed her slit with the tip, Miru-chan answered
 while exhaling hot breaths.</t>
         </is>
       </c>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="B1292" s="1" t="inlineStr">
         <is>
-          <t>「…Yeah. It'll probably turn out that way, you know？」</t>
+          <t>…Yeah. It'll probably turn out that way, you know？</t>
         </is>
       </c>
       <c r="C1292" t="n">
@@ -20364,8 +20364,8 @@
       </c>
       <c r="B1300" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... but it's still embarrassing, so you don't
-have to do anything extra, okay？」</t>
+          <t>Yeah... but it's still embarrassing, so you don't
+have to do anything extra, okay？</t>
         </is>
       </c>
       <c r="C1300" t="n">
@@ -20747,8 +20747,8 @@
       </c>
       <c r="B1325" s="1" t="inlineStr">
         <is>
-          <t>No wonder — the vagina I'd thought was tight was
-actually soft and just kept swallowing my penis more
+          <t>No wonder — the vagina he'd thought was tight was
+actually soft and just kept swallowing his penis more
 and more.</t>
         </is>
       </c>
@@ -21131,8 +21131,8 @@
       </c>
       <c r="B1350" s="1" t="inlineStr">
         <is>
-          <t>「Oh... then, shall we stay still until you get used
-to it？」</t>
+          <t>Oh... then, shall we stay still until you get used to
+it？</t>
         </is>
       </c>
       <c r="C1350" t="n">
@@ -21346,7 +21346,7 @@
       </c>
       <c r="B1364" s="1" t="inlineStr">
         <is>
-          <t>「Nnah！ Auh, uuh！ Kk, huff... kuu. U... uuh... akya！」</t>
+          <t>Nnah！ Auh, uuh！ Kk, huff... kuu. U... uuh... akya！</t>
         </is>
       </c>
       <c r="C1364" t="n">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="B1366" s="1" t="inlineStr">
         <is>
-          <t>「Ah... aaah...！！」</t>
+          <t>Ah... aaah...！！</t>
         </is>
       </c>
       <c r="C1366" t="n">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="B1448" s="1" t="inlineStr">
         <is>
-          <t>「Ah... you really do understand, don't you？」</t>
+          <t>Ah... you really do understand, don't you？</t>
         </is>
       </c>
       <c r="C1448" t="n">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="B1463" s="1" t="inlineStr">
         <is>
-          <t>I pulled my penis back up near the entrance of the
+          <t>He pulled his penis back up near the entrance of the
 vaginal canal and it seemed okay to rub along the
 tight spot.</t>
         </is>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="B1471" s="1" t="inlineStr">
         <is>
-          <t>「Well then, wanna try a few more things？」</t>
+          <t>Well then, wanna try a few more things？</t>
         </is>
       </c>
       <c r="C1471" t="n">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="B1473" s="1" t="inlineStr">
         <is>
-          <t>「Ugh！？ Nn, nngh, uuh...！？ Ah, ah... u！ Hah, haaa...！」</t>
+          <t>Ugh！？ Nn, nngh, uuh...！？ Ah, ah... u！ Hah, haaa...！</t>
         </is>
       </c>
       <c r="C1473" t="n">
@@ -23027,8 +23027,9 @@
       </c>
       <c r="B1474" s="1" t="inlineStr">
         <is>
-          <t>I pull back my hips and thrust, then thrust and pull
-back, carefully stirring around inside her pussy.</t>
+          <t>He pulls back his hips and thrusts, then thrusts and
+pulls back, carefully stirring around inside her
+pussy.</t>
         </is>
       </c>
       <c r="C1474" t="n">
@@ -23164,8 +23165,8 @@
       </c>
       <c r="B1483" s="1" t="inlineStr">
         <is>
-          <t>「Nngh！ Ngh！ Nnngh~！？ Ppah！ Hah... hah, hah...n！ Ngh！
-Ngh！」</t>
+          <t>Nngh！ Ngh！ Nnngh~！？ Ppah！ Hah... hah, hah...n！ Ngh！
+Ngh！</t>
         </is>
       </c>
       <c r="C1483" t="n">
@@ -24319,7 +24320,7 @@
       </c>
       <c r="B1558" s="1" t="inlineStr">
         <is>
-          <t>I thrust deep into her with long strokes, rubbing
+          <t>He thrusts deep into her with long strokes, rubbing
 every inch from the entrance to the deepest part of
 her vagina…</t>
         </is>
@@ -24457,7 +24458,7 @@
       </c>
       <c r="B1567" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... mm...！」</t>
+          <t>Ugh... mm...！</t>
         </is>
       </c>
       <c r="C1567" t="n">
@@ -24594,7 +24595,7 @@
       </c>
       <c r="B1576" s="1" t="inlineStr">
         <is>
-          <t>Semen rushes through the center of my penis.</t>
+          <t>Semen rushes through the center of his penis.</t>
         </is>
       </c>
       <c r="C1576" t="n">
@@ -24609,7 +24610,7 @@
       </c>
       <c r="B1577" s="1" t="inlineStr">
         <is>
-          <t>The impact makes my head go completely blank….</t>
+          <t>The impact makes his head go completely blank….</t>
         </is>
       </c>
       <c r="C1577" t="n">
@@ -24701,7 +24702,7 @@
       </c>
       <c r="B1583" s="1" t="inlineStr">
         <is>
-          <t>Could it be that you came from me ejaculating inside
+          <t>Could it be that you came from him ejaculating inside
 you...？</t>
         </is>
       </c>
@@ -25691,7 +25692,7 @@
       </c>
       <c r="B1648" s="1" t="inlineStr">
         <is>
-          <t>「I felt way, way better！」</t>
+          <t>I felt way, way better！</t>
         </is>
       </c>
       <c r="C1648" t="n">
@@ -25768,7 +25769,7 @@
       </c>
       <c r="B1653" s="1" t="inlineStr">
         <is>
-          <t>「Hey... do you think I could get pregnant from this？」</t>
+          <t>Hey... do you think I could get pregnant from this？</t>
         </is>
       </c>
       <c r="C1653" t="n">
@@ -25828,7 +25829,7 @@
       </c>
       <c r="B1657" s="1" t="inlineStr">
         <is>
-          <t>「Mm？ Who are you saying 'is here'？」</t>
+          <t>Mm？ Who are you saying 'is here'？</t>
         </is>
       </c>
       <c r="C1657" t="n">
@@ -25920,7 +25921,7 @@
       </c>
       <c r="B1663" s="1" t="inlineStr">
         <is>
-          <t>「No… I've never been like that.」</t>
+          <t>No… I've never been like that.</t>
         </is>
       </c>
       <c r="C1663" t="n">
@@ -25950,8 +25951,8 @@
       </c>
       <c r="B1665" s="1" t="inlineStr">
         <is>
-          <t>「W-well, does that mean we still can't have a baby
-yet...？」</t>
+          <t>W-well, does that mean we still can't have a baby
+yet...？</t>
         </is>
       </c>
       <c r="C1665" t="n">
